--- a/recog_phase.xlsx
+++ b/recog_phase.xlsx
@@ -623,79 +623,79 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>-177</v>
+        <v>-258</v>
       </c>
       <c r="B2">
-        <v>-126</v>
+        <v>-195</v>
       </c>
       <c r="C2">
-        <v>-71</v>
+        <v>-340</v>
       </c>
       <c r="D2">
-        <v>-78</v>
+        <v>-111</v>
       </c>
       <c r="E2">
-        <v>-229</v>
+        <v>-259</v>
       </c>
       <c r="F2">
-        <v>-173</v>
+        <v>-43</v>
       </c>
       <c r="G2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="H2">
-        <v>173</v>
+        <v>41</v>
       </c>
       <c r="I2">
-        <v>228</v>
+        <v>180</v>
       </c>
       <c r="J2">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="K2">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="L2">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="M2">
-        <v>-22</v>
+        <v>-32</v>
       </c>
       <c r="N2">
-        <v>-225</v>
+        <v>-266</v>
       </c>
       <c r="O2">
-        <v>-123</v>
+        <v>-194</v>
       </c>
       <c r="P2">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="Q2">
-        <v>173</v>
+        <v>343</v>
       </c>
       <c r="R2">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="S2">
-        <v>-224</v>
+        <v>-43</v>
       </c>
       <c r="T2">
-        <v>-178</v>
+        <v>-188</v>
       </c>
       <c r="U2">
-        <v>-27</v>
+        <v>-107</v>
       </c>
       <c r="V2">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="W2">
-        <v>177</v>
+        <v>118</v>
       </c>
       <c r="X2">
-        <v>225</v>
+        <v>34</v>
       </c>
       <c r="Y2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -704,31 +704,31 @@
         <v>180</v>
       </c>
       <c r="AB2">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AC2">
         <v>270</v>
       </c>
       <c r="AD2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF2">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AG2">
         <v>90</v>
       </c>
       <c r="AH2">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AJ2">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -752,12 +752,12 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -791,96 +791,101 @@
         </is>
       </c>
       <c r="AW2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>old</t>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>-222</v>
+        <v>-34</v>
       </c>
       <c r="B3">
-        <v>-74</v>
+        <v>-182</v>
       </c>
       <c r="C3">
-        <v>-30</v>
+        <v>-112</v>
       </c>
       <c r="D3">
-        <v>-225</v>
+        <v>-259</v>
       </c>
       <c r="E3">
-        <v>-175</v>
+        <v>-338</v>
       </c>
       <c r="F3">
-        <v>-80</v>
+        <v>-41</v>
       </c>
       <c r="G3">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H3">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="I3">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="J3">
-        <v>22</v>
+        <v>258</v>
       </c>
       <c r="K3">
-        <v>178</v>
+        <v>340</v>
       </c>
       <c r="L3">
-        <v>220</v>
+        <v>31</v>
       </c>
       <c r="M3">
-        <v>-173</v>
+        <v>-189</v>
       </c>
       <c r="N3">
-        <v>-76</v>
+        <v>-118</v>
       </c>
       <c r="O3">
-        <v>-125</v>
+        <v>-338</v>
       </c>
       <c r="P3">
-        <v>29</v>
+        <v>258</v>
       </c>
       <c r="Q3">
-        <v>129</v>
+        <v>330</v>
       </c>
       <c r="R3">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="S3">
-        <v>-75</v>
+        <v>-115</v>
       </c>
       <c r="T3">
-        <v>-171</v>
+        <v>-38</v>
       </c>
       <c r="U3">
-        <v>-230</v>
+        <v>-269</v>
       </c>
       <c r="V3">
-        <v>221</v>
+        <v>44</v>
       </c>
       <c r="W3">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="X3">
-        <v>29</v>
+        <v>334</v>
       </c>
       <c r="Y3">
         <v>180</v>
@@ -889,19 +894,19 @@
         <v>90</v>
       </c>
       <c r="AA3">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AB3">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AC3">
         <v>270</v>
       </c>
       <c r="AD3">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -910,13 +915,13 @@
         <v>180</v>
       </c>
       <c r="AH3">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ3">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -1004,293 +1009,288 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>-225</v>
+        <v>-31</v>
       </c>
       <c r="B4">
-        <v>-24</v>
+        <v>-342</v>
       </c>
       <c r="C4">
-        <v>-120</v>
+        <v>-117</v>
       </c>
       <c r="D4">
-        <v>-128</v>
+        <v>-260</v>
       </c>
       <c r="E4">
-        <v>-78</v>
+        <v>-187</v>
       </c>
       <c r="F4">
-        <v>-222</v>
+        <v>-36</v>
       </c>
       <c r="G4">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="H4">
-        <v>125</v>
+        <v>263</v>
       </c>
       <c r="I4">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="J4">
-        <v>176</v>
+        <v>259</v>
       </c>
       <c r="K4">
-        <v>229</v>
+        <v>120</v>
       </c>
       <c r="L4">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="M4">
-        <v>-71</v>
+        <v>-110</v>
       </c>
       <c r="N4">
-        <v>-28</v>
+        <v>-32</v>
       </c>
       <c r="O4">
-        <v>-221</v>
+        <v>-256</v>
       </c>
       <c r="P4">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="Q4">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="R4">
-        <v>71</v>
+        <v>261</v>
       </c>
       <c r="S4">
-        <v>-71</v>
+        <v>-343</v>
       </c>
       <c r="T4">
-        <v>-122</v>
+        <v>-116</v>
       </c>
       <c r="U4">
-        <v>-225</v>
+        <v>-258</v>
       </c>
       <c r="V4">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="W4">
-        <v>224</v>
+        <v>341</v>
       </c>
       <c r="X4">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="Y4">
         <v>90</v>
       </c>
       <c r="Z4">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AB4">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AC4">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AE4">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AG4">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AH4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AJ4">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>L0.png</t>
         </is>
       </c>
       <c r="AW4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
           <t>left</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>right</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>-75</v>
+        <v>-334</v>
       </c>
       <c r="B5">
-        <v>-176</v>
+        <v>-118</v>
       </c>
       <c r="C5">
-        <v>-224</v>
+        <v>-193</v>
       </c>
       <c r="D5">
-        <v>-129</v>
+        <v>-334</v>
       </c>
       <c r="E5">
-        <v>-225</v>
+        <v>-257</v>
       </c>
       <c r="F5">
-        <v>-80</v>
+        <v>-184</v>
       </c>
       <c r="G5">
-        <v>170</v>
+        <v>336</v>
       </c>
       <c r="H5">
-        <v>230</v>
+        <v>182</v>
       </c>
       <c r="I5">
-        <v>25</v>
+        <v>259</v>
       </c>
       <c r="J5">
-        <v>124</v>
+        <v>266</v>
       </c>
       <c r="K5">
-        <v>172</v>
+        <v>113</v>
       </c>
       <c r="L5">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="M5">
-        <v>-121</v>
+        <v>-108</v>
       </c>
       <c r="N5">
-        <v>-227</v>
+        <v>-192</v>
       </c>
       <c r="O5">
-        <v>-25</v>
+        <v>-270</v>
       </c>
       <c r="P5">
-        <v>128</v>
+        <v>193</v>
       </c>
       <c r="Q5">
-        <v>226</v>
+        <v>113</v>
       </c>
       <c r="R5">
-        <v>170</v>
+        <v>334</v>
       </c>
       <c r="S5">
-        <v>-30</v>
+        <v>-34</v>
       </c>
       <c r="T5">
-        <v>-173</v>
+        <v>-334</v>
       </c>
       <c r="U5">
-        <v>-127</v>
+        <v>-106</v>
       </c>
       <c r="V5">
-        <v>29</v>
+        <v>185</v>
       </c>
       <c r="W5">
-        <v>226</v>
+        <v>334</v>
       </c>
       <c r="X5">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="Y5">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="Z5">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AA5">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AC5">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AF5">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AG5">
         <v>180</v>
@@ -1299,14 +1299,14 @@
         <v>90</v>
       </c>
       <c r="AI5">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="AW5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1374,125 +1374,120 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>new</t>
+          <t>old</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>-127</v>
+        <v>-39</v>
       </c>
       <c r="B6">
-        <v>-25</v>
+        <v>-186</v>
       </c>
       <c r="C6">
-        <v>-221</v>
+        <v>-115</v>
       </c>
       <c r="D6">
-        <v>-180</v>
+        <v>-111</v>
       </c>
       <c r="E6">
-        <v>-77</v>
+        <v>-258</v>
       </c>
       <c r="F6">
-        <v>-123</v>
+        <v>-343</v>
       </c>
       <c r="G6">
-        <v>223</v>
+        <v>110</v>
       </c>
       <c r="H6">
-        <v>74</v>
+        <v>338</v>
       </c>
       <c r="I6">
-        <v>124</v>
+        <v>187</v>
       </c>
       <c r="J6">
-        <v>27</v>
+        <v>183</v>
       </c>
       <c r="K6">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="L6">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="M6">
-        <v>-126</v>
+        <v>-333</v>
       </c>
       <c r="N6">
-        <v>-26</v>
+        <v>-256</v>
       </c>
       <c r="O6">
-        <v>-77</v>
+        <v>-193</v>
       </c>
       <c r="P6">
-        <v>224</v>
+        <v>109</v>
       </c>
       <c r="Q6">
-        <v>25</v>
+        <v>264</v>
       </c>
       <c r="R6">
-        <v>174</v>
+        <v>39</v>
       </c>
       <c r="S6">
-        <v>-27</v>
+        <v>-110</v>
       </c>
       <c r="T6">
-        <v>-123</v>
+        <v>-183</v>
       </c>
       <c r="U6">
-        <v>-80</v>
+        <v>-340</v>
       </c>
       <c r="V6">
-        <v>122</v>
+        <v>258</v>
       </c>
       <c r="W6">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="X6">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="Y6">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="Z6">
         <v>270</v>
       </c>
       <c r="AA6">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AB6">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AD6">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF6">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AG6">
         <v>180</v>
       </c>
       <c r="AH6">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AJ6">
         <v>270</v>
@@ -1549,16 +1544,16 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1567,101 +1562,96 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>new</t>
+          <t>old</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>-129</v>
+        <v>-106</v>
       </c>
       <c r="B7">
-        <v>-174</v>
+        <v>-344</v>
       </c>
       <c r="C7">
-        <v>-222</v>
+        <v>-189</v>
       </c>
       <c r="D7">
-        <v>-25</v>
+        <v>-109</v>
       </c>
       <c r="E7">
-        <v>-122</v>
+        <v>-330</v>
       </c>
       <c r="F7">
-        <v>-230</v>
+        <v>-257</v>
       </c>
       <c r="G7">
-        <v>173</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="I7">
-        <v>128</v>
+        <v>257</v>
       </c>
       <c r="J7">
-        <v>227</v>
+        <v>268</v>
       </c>
       <c r="K7">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="L7">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="M7">
-        <v>-170</v>
+        <v>-30</v>
       </c>
       <c r="N7">
-        <v>-128</v>
+        <v>-186</v>
       </c>
       <c r="O7">
-        <v>-220</v>
+        <v>-266</v>
       </c>
       <c r="P7">
-        <v>126</v>
+        <v>259</v>
       </c>
       <c r="Q7">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="R7">
-        <v>226</v>
+        <v>106</v>
       </c>
       <c r="S7">
-        <v>-226</v>
+        <v>-194</v>
       </c>
       <c r="T7">
-        <v>-23</v>
+        <v>-44</v>
       </c>
       <c r="U7">
-        <v>-176</v>
+        <v>-117</v>
       </c>
       <c r="V7">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="W7">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="X7">
-        <v>171</v>
+        <v>256</v>
       </c>
       <c r="Y7">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="Z7">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AB7">
         <v>90</v>
@@ -1670,13 +1660,13 @@
         <v>90</v>
       </c>
       <c r="AD7">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AG7">
         <v>270</v>
@@ -1688,7 +1678,7 @@
         <v>270</v>
       </c>
       <c r="AJ7">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
@@ -1712,176 +1702,171 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>L0.png</t>
         </is>
       </c>
       <c r="AW7">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
           <t>left</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>right</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>-128</v>
+        <v>-269</v>
       </c>
       <c r="B8">
-        <v>-74</v>
+        <v>-38</v>
       </c>
       <c r="C8">
-        <v>-177</v>
+        <v>-115</v>
       </c>
       <c r="D8">
-        <v>-178</v>
+        <v>-268</v>
       </c>
       <c r="E8">
-        <v>-25</v>
+        <v>-31</v>
       </c>
       <c r="F8">
-        <v>-226</v>
+        <v>-116</v>
       </c>
       <c r="G8">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="H8">
-        <v>177</v>
+        <v>33</v>
       </c>
       <c r="I8">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="J8">
-        <v>221</v>
+        <v>270</v>
       </c>
       <c r="K8">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="L8">
-        <v>30</v>
+        <v>336</v>
       </c>
       <c r="M8">
-        <v>-173</v>
+        <v>-186</v>
       </c>
       <c r="N8">
-        <v>-78</v>
+        <v>-34</v>
       </c>
       <c r="O8">
-        <v>-225</v>
+        <v>-344</v>
       </c>
       <c r="P8">
-        <v>121</v>
+        <v>182</v>
       </c>
       <c r="Q8">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="R8">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="S8">
-        <v>-30</v>
+        <v>-339</v>
       </c>
       <c r="T8">
-        <v>-223</v>
+        <v>-36</v>
       </c>
       <c r="U8">
-        <v>-129</v>
+        <v>-256</v>
       </c>
       <c r="V8">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="W8">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="X8">
-        <v>178</v>
+        <v>331</v>
       </c>
       <c r="Y8">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="Z8">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AA8">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AC8">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AF8">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AI8">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
@@ -1920,19 +1905,19 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AU8" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -1944,7 +1929,7 @@
         </is>
       </c>
       <c r="AW8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -1964,112 +1949,112 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>-229</v>
+        <v>-41</v>
       </c>
       <c r="B9">
-        <v>-79</v>
+        <v>-117</v>
       </c>
       <c r="C9">
-        <v>-175</v>
+        <v>-190</v>
       </c>
       <c r="D9">
-        <v>-80</v>
+        <v>-332</v>
       </c>
       <c r="E9">
-        <v>-124</v>
+        <v>-108</v>
       </c>
       <c r="F9">
-        <v>-25</v>
+        <v>-267</v>
       </c>
       <c r="G9">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="H9">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I9">
-        <v>223</v>
+        <v>117</v>
       </c>
       <c r="J9">
-        <v>223</v>
+        <v>109</v>
       </c>
       <c r="K9">
-        <v>24</v>
+        <v>335</v>
       </c>
       <c r="L9">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="M9">
-        <v>-221</v>
+        <v>-259</v>
       </c>
       <c r="N9">
-        <v>-21</v>
+        <v>-37</v>
       </c>
       <c r="O9">
-        <v>-78</v>
+        <v>-341</v>
       </c>
       <c r="P9">
-        <v>223</v>
+        <v>338</v>
       </c>
       <c r="Q9">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="R9">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="S9">
-        <v>-79</v>
+        <v>-337</v>
       </c>
       <c r="T9">
-        <v>-173</v>
+        <v>-31</v>
       </c>
       <c r="U9">
-        <v>-21</v>
+        <v>-115</v>
       </c>
       <c r="V9">
-        <v>78</v>
+        <v>336</v>
       </c>
       <c r="W9">
-        <v>126</v>
+        <v>189</v>
       </c>
       <c r="X9">
-        <v>227</v>
+        <v>34</v>
       </c>
       <c r="Y9">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="Z9">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AA9">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AB9">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AC9">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AE9">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ9">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
@@ -2088,180 +2073,185 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AW9">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>old</t>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>-226</v>
+        <v>-36</v>
       </c>
       <c r="B10">
-        <v>-174</v>
+        <v>-344</v>
       </c>
       <c r="C10">
-        <v>-25</v>
+        <v>-110</v>
       </c>
       <c r="D10">
-        <v>-126</v>
+        <v>-334</v>
       </c>
       <c r="E10">
-        <v>-172</v>
+        <v>-186</v>
       </c>
       <c r="F10">
-        <v>-28</v>
+        <v>-107</v>
       </c>
       <c r="G10">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="H10">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="I10">
-        <v>75</v>
+        <v>267</v>
       </c>
       <c r="J10">
-        <v>76</v>
+        <v>262</v>
       </c>
       <c r="K10">
-        <v>173</v>
+        <v>108</v>
       </c>
       <c r="L10">
-        <v>226</v>
+        <v>37</v>
       </c>
       <c r="M10">
-        <v>-224</v>
+        <v>-257</v>
       </c>
       <c r="N10">
-        <v>-124</v>
+        <v>-42</v>
       </c>
       <c r="O10">
-        <v>-72</v>
+        <v>-193</v>
       </c>
       <c r="P10">
-        <v>176</v>
+        <v>37</v>
       </c>
       <c r="Q10">
-        <v>80</v>
+        <v>331</v>
       </c>
       <c r="R10">
-        <v>224</v>
+        <v>117</v>
       </c>
       <c r="S10">
-        <v>-179</v>
+        <v>-42</v>
       </c>
       <c r="T10">
-        <v>-27</v>
+        <v>-338</v>
       </c>
       <c r="U10">
-        <v>-70</v>
+        <v>-191</v>
       </c>
       <c r="V10">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="W10">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="X10">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="Y10">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="Z10">
         <v>180</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AB10">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AC10">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AD10">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AF10">
         <v>270</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AH10">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -2281,7 +2271,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2320,7 +2310,7 @@
         </is>
       </c>
       <c r="AW10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2345,109 +2335,109 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>-220</v>
+        <v>-38</v>
       </c>
       <c r="B11">
-        <v>-23</v>
+        <v>-341</v>
       </c>
       <c r="C11">
-        <v>-171</v>
+        <v>-186</v>
       </c>
       <c r="D11">
-        <v>-174</v>
+        <v>-40</v>
       </c>
       <c r="E11">
-        <v>-22</v>
+        <v>-114</v>
       </c>
       <c r="F11">
-        <v>-229</v>
+        <v>-343</v>
       </c>
       <c r="G11">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="H11">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="I11">
-        <v>73</v>
+        <v>338</v>
       </c>
       <c r="J11">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="K11">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="L11">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="M11">
-        <v>-173</v>
+        <v>-31</v>
       </c>
       <c r="N11">
-        <v>-70</v>
+        <v>-113</v>
       </c>
       <c r="O11">
-        <v>-123</v>
+        <v>-257</v>
       </c>
       <c r="P11">
-        <v>224</v>
+        <v>339</v>
       </c>
       <c r="Q11">
-        <v>23</v>
+        <v>190</v>
       </c>
       <c r="R11">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="S11">
-        <v>-180</v>
+        <v>-336</v>
       </c>
       <c r="T11">
-        <v>-130</v>
+        <v>-40</v>
       </c>
       <c r="U11">
-        <v>-79</v>
+        <v>-108</v>
       </c>
       <c r="V11">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="W11">
-        <v>222</v>
+        <v>270</v>
       </c>
       <c r="X11">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="Y11">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AC11">
         <v>90</v>
       </c>
       <c r="AD11">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AE11">
         <v>180</v>
       </c>
       <c r="AF11">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AH11">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AI11">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
         <v>90</v>
@@ -2489,7 +2479,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2509,127 +2499,132 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW11">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>old</t>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>-75</v>
+        <v>-191</v>
       </c>
       <c r="B12">
-        <v>-121</v>
+        <v>-108</v>
       </c>
       <c r="C12">
-        <v>-222</v>
+        <v>-344</v>
       </c>
       <c r="D12">
-        <v>-230</v>
+        <v>-265</v>
       </c>
       <c r="E12">
-        <v>-71</v>
+        <v>-118</v>
       </c>
       <c r="F12">
-        <v>-23</v>
+        <v>-44</v>
       </c>
       <c r="G12">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="H12">
-        <v>225</v>
+        <v>39</v>
       </c>
       <c r="I12">
-        <v>176</v>
+        <v>340</v>
       </c>
       <c r="J12">
-        <v>74</v>
+        <v>267</v>
       </c>
       <c r="K12">
-        <v>21</v>
+        <v>343</v>
       </c>
       <c r="L12">
-        <v>223</v>
+        <v>43</v>
       </c>
       <c r="M12">
-        <v>-120</v>
+        <v>-344</v>
       </c>
       <c r="N12">
-        <v>-77</v>
+        <v>-37</v>
       </c>
       <c r="O12">
-        <v>-223</v>
+        <v>-269</v>
       </c>
       <c r="P12">
-        <v>120</v>
+        <v>262</v>
       </c>
       <c r="Q12">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="R12">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="S12">
-        <v>-179</v>
+        <v>-112</v>
       </c>
       <c r="T12">
-        <v>-72</v>
+        <v>-267</v>
       </c>
       <c r="U12">
-        <v>-28</v>
+        <v>-187</v>
       </c>
       <c r="V12">
-        <v>77</v>
+        <v>266</v>
       </c>
       <c r="W12">
-        <v>120</v>
+        <v>187</v>
       </c>
       <c r="X12">
-        <v>224</v>
+        <v>39</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AA12">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AB12">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AF12">
         <v>270</v>
       </c>
       <c r="AG12">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AH12">
         <v>90</v>
@@ -2638,7 +2633,7 @@
         <v>90</v>
       </c>
       <c r="AJ12">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
@@ -2667,7 +2662,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2697,15 +2692,15 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW12">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2721,112 +2716,112 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>-76</v>
+        <v>-111</v>
       </c>
       <c r="B13">
-        <v>-123</v>
+        <v>-269</v>
       </c>
       <c r="C13">
-        <v>-25</v>
+        <v>-331</v>
       </c>
       <c r="D13">
-        <v>-76</v>
+        <v>-40</v>
       </c>
       <c r="E13">
-        <v>-127</v>
+        <v>-118</v>
       </c>
       <c r="F13">
-        <v>-175</v>
+        <v>-263</v>
       </c>
       <c r="G13">
-        <v>226</v>
+        <v>188</v>
       </c>
       <c r="H13">
-        <v>170</v>
+        <v>345</v>
       </c>
       <c r="I13">
-        <v>126</v>
+        <v>268</v>
       </c>
       <c r="J13">
-        <v>229</v>
+        <v>341</v>
       </c>
       <c r="K13">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="L13">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="M13">
-        <v>-171</v>
+        <v>-111</v>
       </c>
       <c r="N13">
-        <v>-228</v>
+        <v>-264</v>
       </c>
       <c r="O13">
-        <v>-26</v>
+        <v>-31</v>
       </c>
       <c r="P13">
-        <v>220</v>
+        <v>34</v>
       </c>
       <c r="Q13">
-        <v>124</v>
+        <v>255</v>
       </c>
       <c r="R13">
-        <v>173</v>
+        <v>336</v>
       </c>
       <c r="S13">
-        <v>-229</v>
+        <v>-195</v>
       </c>
       <c r="T13">
-        <v>-71</v>
+        <v>-335</v>
       </c>
       <c r="U13">
-        <v>-177</v>
+        <v>-37</v>
       </c>
       <c r="V13">
-        <v>27</v>
+        <v>264</v>
       </c>
       <c r="W13">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="X13">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="Y13">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="Z13">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AA13">
         <v>180</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AE13">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AF13">
         <v>90</v>
       </c>
       <c r="AG13">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AI13">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
@@ -2845,7 +2840,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2870,7 +2865,7 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
@@ -2889,7 +2884,7 @@
         </is>
       </c>
       <c r="AW13">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
@@ -2909,88 +2904,88 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>-171</v>
+        <v>-110</v>
       </c>
       <c r="B14">
-        <v>-228</v>
+        <v>-41</v>
       </c>
       <c r="C14">
-        <v>-127</v>
+        <v>-185</v>
       </c>
       <c r="D14">
-        <v>-78</v>
+        <v>-106</v>
       </c>
       <c r="E14">
-        <v>-175</v>
+        <v>-32</v>
       </c>
       <c r="F14">
-        <v>-20</v>
+        <v>-259</v>
       </c>
       <c r="G14">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="H14">
-        <v>76</v>
+        <v>259</v>
       </c>
       <c r="I14">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="J14">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="K14">
-        <v>71</v>
+        <v>262</v>
       </c>
       <c r="L14">
-        <v>224</v>
+        <v>333</v>
       </c>
       <c r="M14">
-        <v>-73</v>
+        <v>-181</v>
       </c>
       <c r="N14">
-        <v>-21</v>
+        <v>-344</v>
       </c>
       <c r="O14">
-        <v>-127</v>
+        <v>-108</v>
       </c>
       <c r="P14">
-        <v>129</v>
+        <v>259</v>
       </c>
       <c r="Q14">
-        <v>176</v>
+        <v>37</v>
       </c>
       <c r="R14">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="S14">
-        <v>-172</v>
+        <v>-184</v>
       </c>
       <c r="T14">
-        <v>-120</v>
+        <v>-263</v>
       </c>
       <c r="U14">
-        <v>-26</v>
+        <v>-44</v>
       </c>
       <c r="V14">
-        <v>174</v>
+        <v>260</v>
       </c>
       <c r="W14">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="X14">
-        <v>122</v>
+        <v>191</v>
       </c>
       <c r="Y14">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AA14">
         <v>90</v>
       </c>
       <c r="AB14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AC14">
         <v>270</v>
@@ -2999,7 +2994,7 @@
         <v>180</v>
       </c>
       <c r="AE14">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AF14">
         <v>90</v>
@@ -3008,10 +3003,10 @@
         <v>270</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AI14">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
         <v>0</v>
@@ -3086,99 +3081,104 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>old</t>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>-20</v>
+        <v>-185</v>
       </c>
       <c r="B15">
-        <v>-177</v>
+        <v>-43</v>
       </c>
       <c r="C15">
-        <v>-73</v>
+        <v>-334</v>
       </c>
       <c r="D15">
-        <v>-178</v>
+        <v>-39</v>
       </c>
       <c r="E15">
-        <v>-124</v>
+        <v>-266</v>
       </c>
       <c r="F15">
-        <v>-228</v>
+        <v>-181</v>
       </c>
       <c r="G15">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="H15">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="I15">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="J15">
-        <v>28</v>
+        <v>340</v>
       </c>
       <c r="K15">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="L15">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="M15">
-        <v>-173</v>
+        <v>-185</v>
       </c>
       <c r="N15">
-        <v>-226</v>
+        <v>-41</v>
       </c>
       <c r="O15">
-        <v>-129</v>
+        <v>-115</v>
       </c>
       <c r="P15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="Q15">
-        <v>129</v>
+        <v>334</v>
       </c>
       <c r="R15">
-        <v>222</v>
+        <v>116</v>
       </c>
       <c r="S15">
-        <v>-171</v>
+        <v>-117</v>
       </c>
       <c r="T15">
-        <v>-29</v>
+        <v>-43</v>
       </c>
       <c r="U15">
-        <v>-129</v>
+        <v>-334</v>
       </c>
       <c r="V15">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="W15">
-        <v>122</v>
+        <v>255</v>
       </c>
       <c r="X15">
-        <v>223</v>
+        <v>106</v>
       </c>
       <c r="Y15">
         <v>90</v>
       </c>
       <c r="Z15">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AA15">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AC15">
         <v>270</v>
@@ -3187,10 +3187,10 @@
         <v>180</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF15">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AG15">
         <v>180</v>
@@ -3199,36 +3199,36 @@
         <v>0</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AJ15">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AP15" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -3265,11 +3265,11 @@
         </is>
       </c>
       <c r="AW15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -3285,106 +3285,106 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>-171</v>
+        <v>-34</v>
       </c>
       <c r="B16">
-        <v>-75</v>
+        <v>-113</v>
       </c>
       <c r="C16">
-        <v>-26</v>
+        <v>-261</v>
       </c>
       <c r="D16">
-        <v>-175</v>
+        <v>-190</v>
       </c>
       <c r="E16">
-        <v>-127</v>
+        <v>-336</v>
       </c>
       <c r="F16">
-        <v>-25</v>
+        <v>-115</v>
       </c>
       <c r="G16">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H16">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="I16">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="J16">
-        <v>174</v>
+        <v>262</v>
       </c>
       <c r="K16">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="L16">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="M16">
-        <v>-171</v>
+        <v>-38</v>
       </c>
       <c r="N16">
-        <v>-29</v>
+        <v>-340</v>
       </c>
       <c r="O16">
-        <v>-227</v>
+        <v>-191</v>
       </c>
       <c r="P16">
-        <v>179</v>
+        <v>337</v>
       </c>
       <c r="Q16">
-        <v>124</v>
+        <v>262</v>
       </c>
       <c r="R16">
-        <v>225</v>
+        <v>35</v>
       </c>
       <c r="S16">
-        <v>-227</v>
+        <v>-336</v>
       </c>
       <c r="T16">
-        <v>-79</v>
+        <v>-260</v>
       </c>
       <c r="U16">
-        <v>-23</v>
+        <v>-120</v>
       </c>
       <c r="V16">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="W16">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="X16">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="Y16">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="Z16">
         <v>270</v>
       </c>
       <c r="AA16">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB16">
         <v>90</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AE16">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AH16">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AI16">
         <v>180</v>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -3449,15 +3449,15 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW16">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -3478,133 +3478,133 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>-225</v>
+        <v>-118</v>
       </c>
       <c r="B17">
-        <v>-179</v>
+        <v>-265</v>
       </c>
       <c r="C17">
-        <v>-77</v>
+        <v>-334</v>
       </c>
       <c r="D17">
-        <v>-220</v>
+        <v>-262</v>
       </c>
       <c r="E17">
-        <v>-124</v>
+        <v>-340</v>
       </c>
       <c r="F17">
-        <v>-21</v>
+        <v>-184</v>
       </c>
       <c r="G17">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="H17">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="I17">
-        <v>27</v>
+        <v>261</v>
       </c>
       <c r="J17">
-        <v>78</v>
+        <v>263</v>
       </c>
       <c r="K17">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="L17">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="M17">
-        <v>-178</v>
+        <v>-42</v>
       </c>
       <c r="N17">
-        <v>-79</v>
+        <v>-258</v>
       </c>
       <c r="O17">
-        <v>-230</v>
+        <v>-184</v>
       </c>
       <c r="P17">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="Q17">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="R17">
-        <v>121</v>
+        <v>267</v>
       </c>
       <c r="S17">
-        <v>-121</v>
+        <v>-180</v>
       </c>
       <c r="T17">
-        <v>-228</v>
+        <v>-116</v>
       </c>
       <c r="U17">
-        <v>-170</v>
+        <v>-332</v>
       </c>
       <c r="V17">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="W17">
-        <v>176</v>
+        <v>262</v>
       </c>
       <c r="X17">
-        <v>22</v>
+        <v>331</v>
       </c>
       <c r="Y17">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="Z17">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AD17">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AG17">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AI17">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AJ17">
         <v>270</v>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -3646,11 +3646,11 @@
         </is>
       </c>
       <c r="AW17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -3666,112 +3666,112 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>-223</v>
+        <v>-33</v>
       </c>
       <c r="B18">
-        <v>-78</v>
+        <v>-194</v>
       </c>
       <c r="C18">
-        <v>-123</v>
+        <v>-108</v>
       </c>
       <c r="D18">
-        <v>-74</v>
+        <v>-260</v>
       </c>
       <c r="E18">
-        <v>-230</v>
+        <v>-40</v>
       </c>
       <c r="F18">
-        <v>-126</v>
+        <v>-336</v>
       </c>
       <c r="G18">
-        <v>224</v>
+        <v>107</v>
       </c>
       <c r="H18">
-        <v>128</v>
+        <v>344</v>
       </c>
       <c r="I18">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="J18">
-        <v>25</v>
+        <v>336</v>
       </c>
       <c r="K18">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="L18">
-        <v>171</v>
+        <v>106</v>
       </c>
       <c r="M18">
-        <v>-178</v>
+        <v>-344</v>
       </c>
       <c r="N18">
-        <v>-225</v>
+        <v>-113</v>
       </c>
       <c r="O18">
-        <v>-22</v>
+        <v>-263</v>
       </c>
       <c r="P18">
-        <v>128</v>
+        <v>260</v>
       </c>
       <c r="Q18">
-        <v>172</v>
+        <v>342</v>
       </c>
       <c r="R18">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="S18">
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="T18">
-        <v>-70</v>
+        <v>-260</v>
       </c>
       <c r="U18">
-        <v>-226</v>
+        <v>-185</v>
       </c>
       <c r="V18">
-        <v>172</v>
+        <v>344</v>
       </c>
       <c r="W18">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="X18">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="Y18">
         <v>90</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AA18">
         <v>270</v>
       </c>
       <c r="AB18">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AC18">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AD18">
         <v>90</v>
       </c>
       <c r="AE18">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AG18">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AI18">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AJ18">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3830,136 +3830,141 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW18">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>old</t>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>-227</v>
+        <v>-267</v>
       </c>
       <c r="B19">
-        <v>-78</v>
+        <v>-115</v>
       </c>
       <c r="C19">
-        <v>-175</v>
+        <v>-339</v>
       </c>
       <c r="D19">
-        <v>-26</v>
+        <v>-333</v>
       </c>
       <c r="E19">
-        <v>-123</v>
+        <v>-189</v>
       </c>
       <c r="F19">
-        <v>-178</v>
+        <v>-108</v>
       </c>
       <c r="G19">
-        <v>72</v>
+        <v>257</v>
       </c>
       <c r="H19">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="I19">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="J19">
-        <v>175</v>
+        <v>342</v>
       </c>
       <c r="K19">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L19">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="M19">
-        <v>-122</v>
+        <v>-266</v>
       </c>
       <c r="N19">
-        <v>-175</v>
+        <v>-343</v>
       </c>
       <c r="O19">
-        <v>-74</v>
+        <v>-110</v>
       </c>
       <c r="P19">
-        <v>129</v>
+        <v>259</v>
       </c>
       <c r="Q19">
-        <v>177</v>
+        <v>108</v>
       </c>
       <c r="R19">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="S19">
-        <v>-228</v>
+        <v>-39</v>
       </c>
       <c r="T19">
-        <v>-78</v>
+        <v>-262</v>
       </c>
       <c r="U19">
-        <v>-174</v>
+        <v>-119</v>
       </c>
       <c r="V19">
-        <v>228</v>
+        <v>333</v>
       </c>
       <c r="W19">
-        <v>130</v>
+        <v>266</v>
       </c>
       <c r="X19">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="Z19">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB19">
         <v>270</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AD19">
         <v>90</v>
       </c>
       <c r="AE19">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AG19">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AH19">
         <v>90</v>
       </c>
       <c r="AI19">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AJ19">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
@@ -4008,12 +4013,12 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4022,137 +4027,132 @@
         </is>
       </c>
       <c r="AW19">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>new</t>
+          <t>old</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>-179</v>
+        <v>-261</v>
       </c>
       <c r="B20">
-        <v>-28</v>
+        <v>-182</v>
       </c>
       <c r="C20">
-        <v>-123</v>
+        <v>-40</v>
       </c>
       <c r="D20">
-        <v>-224</v>
+        <v>-109</v>
       </c>
       <c r="E20">
-        <v>-27</v>
+        <v>-267</v>
       </c>
       <c r="F20">
-        <v>-180</v>
+        <v>-35</v>
       </c>
       <c r="G20">
-        <v>228</v>
+        <v>344</v>
       </c>
       <c r="H20">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="I20">
-        <v>71</v>
+        <v>195</v>
       </c>
       <c r="J20">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="K20">
-        <v>172</v>
+        <v>32</v>
       </c>
       <c r="L20">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="M20">
-        <v>-77</v>
+        <v>-260</v>
       </c>
       <c r="N20">
-        <v>-29</v>
+        <v>-31</v>
       </c>
       <c r="O20">
-        <v>-126</v>
+        <v>-106</v>
       </c>
       <c r="P20">
-        <v>124</v>
+        <v>270</v>
       </c>
       <c r="Q20">
-        <v>77</v>
+        <v>331</v>
       </c>
       <c r="R20">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="S20">
-        <v>-28</v>
+        <v>-31</v>
       </c>
       <c r="T20">
-        <v>-173</v>
+        <v>-342</v>
       </c>
       <c r="U20">
-        <v>-130</v>
+        <v>-269</v>
       </c>
       <c r="V20">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="W20">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="X20">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="Y20">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="Z20">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AB20">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AC20">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AD20">
         <v>180</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AG20">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AH20">
         <v>90</v>
       </c>
       <c r="AI20">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
@@ -4201,137 +4201,142 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AW20">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>old</t>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>-120</v>
+        <v>-341</v>
       </c>
       <c r="B21">
-        <v>-223</v>
+        <v>-183</v>
       </c>
       <c r="C21">
-        <v>-70</v>
+        <v>-38</v>
       </c>
       <c r="D21">
-        <v>-223</v>
+        <v>-185</v>
       </c>
       <c r="E21">
-        <v>-24</v>
+        <v>-333</v>
       </c>
       <c r="F21">
-        <v>-122</v>
+        <v>-114</v>
       </c>
       <c r="G21">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="H21">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="I21">
-        <v>180</v>
+        <v>332</v>
       </c>
       <c r="J21">
-        <v>123</v>
+        <v>331</v>
       </c>
       <c r="K21">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="L21">
-        <v>174</v>
+        <v>31</v>
       </c>
       <c r="M21">
-        <v>-75</v>
+        <v>-344</v>
       </c>
       <c r="N21">
-        <v>-23</v>
+        <v>-116</v>
       </c>
       <c r="O21">
-        <v>-227</v>
+        <v>-31</v>
       </c>
       <c r="P21">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="Q21">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="R21">
-        <v>174</v>
+        <v>258</v>
       </c>
       <c r="S21">
-        <v>-129</v>
+        <v>-339</v>
       </c>
       <c r="T21">
-        <v>-179</v>
+        <v>-34</v>
       </c>
       <c r="U21">
-        <v>-25</v>
+        <v>-119</v>
       </c>
       <c r="V21">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="W21">
-        <v>225</v>
+        <v>39</v>
       </c>
       <c r="X21">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="Y21">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AC21">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AD21">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AE21">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AF21">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AH21">
         <v>0</v>
@@ -4340,7 +4345,7 @@
         <v>180</v>
       </c>
       <c r="AJ21">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
@@ -4354,19 +4359,19 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AP21" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -4403,11 +4408,11 @@
         </is>
       </c>
       <c r="AW21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -4428,116 +4433,116 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>-221</v>
+        <v>-267</v>
       </c>
       <c r="B22">
-        <v>-175</v>
+        <v>-108</v>
       </c>
       <c r="C22">
-        <v>-23</v>
+        <v>-32</v>
       </c>
       <c r="D22">
-        <v>-75</v>
+        <v>-40</v>
       </c>
       <c r="E22">
-        <v>-173</v>
+        <v>-181</v>
       </c>
       <c r="F22">
-        <v>-24</v>
+        <v>-113</v>
       </c>
       <c r="G22">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="H22">
-        <v>173</v>
+        <v>262</v>
       </c>
       <c r="I22">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J22">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="K22">
-        <v>124</v>
+        <v>339</v>
       </c>
       <c r="L22">
-        <v>175</v>
+        <v>267</v>
       </c>
       <c r="M22">
-        <v>-229</v>
+        <v>-260</v>
       </c>
       <c r="N22">
-        <v>-129</v>
+        <v>-184</v>
       </c>
       <c r="O22">
-        <v>-73</v>
+        <v>-108</v>
       </c>
       <c r="P22">
-        <v>29</v>
+        <v>265</v>
       </c>
       <c r="Q22">
-        <v>229</v>
+        <v>338</v>
       </c>
       <c r="R22">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="S22">
-        <v>-73</v>
+        <v>-32</v>
       </c>
       <c r="T22">
-        <v>-122</v>
+        <v>-116</v>
       </c>
       <c r="U22">
-        <v>-222</v>
+        <v>-194</v>
       </c>
       <c r="V22">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="W22">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="X22">
-        <v>226</v>
+        <v>331</v>
       </c>
       <c r="Y22">
         <v>270</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AA22">
         <v>270</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AC22">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AD22">
         <v>180</v>
       </c>
       <c r="AE22">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AF22">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AG22">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AI22">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ22">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -4567,7 +4572,7 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -4596,137 +4601,132 @@
         </is>
       </c>
       <c r="AW22">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
           <t>left</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>right</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>-180</v>
+        <v>-270</v>
       </c>
       <c r="B23">
-        <v>-124</v>
+        <v>-343</v>
       </c>
       <c r="C23">
-        <v>-230</v>
+        <v>-41</v>
       </c>
       <c r="D23">
-        <v>-179</v>
+        <v>-186</v>
       </c>
       <c r="E23">
-        <v>-71</v>
+        <v>-263</v>
       </c>
       <c r="F23">
-        <v>-128</v>
+        <v>-332</v>
       </c>
       <c r="G23">
-        <v>129</v>
+        <v>255</v>
       </c>
       <c r="H23">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="I23">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="J23">
-        <v>22</v>
+        <v>259</v>
       </c>
       <c r="K23">
-        <v>127</v>
+        <v>335</v>
       </c>
       <c r="L23">
-        <v>178</v>
+        <v>43</v>
       </c>
       <c r="M23">
-        <v>-179</v>
+        <v>-185</v>
       </c>
       <c r="N23">
-        <v>-230</v>
+        <v>-118</v>
       </c>
       <c r="O23">
-        <v>-128</v>
+        <v>-262</v>
       </c>
       <c r="P23">
-        <v>220</v>
+        <v>331</v>
       </c>
       <c r="Q23">
-        <v>173</v>
+        <v>36</v>
       </c>
       <c r="R23">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="S23">
-        <v>-123</v>
+        <v>-109</v>
       </c>
       <c r="T23">
-        <v>-78</v>
+        <v>-333</v>
       </c>
       <c r="U23">
-        <v>-177</v>
+        <v>-36</v>
       </c>
       <c r="V23">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="W23">
-        <v>79</v>
+        <v>268</v>
       </c>
       <c r="X23">
-        <v>174</v>
+        <v>336</v>
       </c>
       <c r="Y23">
         <v>0</v>
       </c>
       <c r="Z23">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AA23">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AB23">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AE23">
         <v>180</v>
       </c>
       <c r="AF23">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AG23">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AH23">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AI23">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AJ23">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
@@ -4789,11 +4789,11 @@
         </is>
       </c>
       <c r="AW23">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -4814,106 +4814,106 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>-174</v>
+        <v>-182</v>
       </c>
       <c r="B24">
-        <v>-75</v>
+        <v>-269</v>
       </c>
       <c r="C24">
-        <v>-23</v>
+        <v>-109</v>
       </c>
       <c r="D24">
-        <v>-222</v>
+        <v>-193</v>
       </c>
       <c r="E24">
-        <v>-24</v>
+        <v>-332</v>
       </c>
       <c r="F24">
-        <v>-127</v>
+        <v>-45</v>
       </c>
       <c r="G24">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="H24">
-        <v>27</v>
+        <v>266</v>
       </c>
       <c r="I24">
-        <v>74</v>
+        <v>334</v>
       </c>
       <c r="J24">
-        <v>122</v>
+        <v>339</v>
       </c>
       <c r="K24">
-        <v>173</v>
+        <v>109</v>
       </c>
       <c r="L24">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="M24">
-        <v>-26</v>
+        <v>-31</v>
       </c>
       <c r="N24">
-        <v>-130</v>
+        <v>-117</v>
       </c>
       <c r="O24">
-        <v>-77</v>
+        <v>-332</v>
       </c>
       <c r="P24">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="Q24">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="R24">
-        <v>124</v>
+        <v>181</v>
       </c>
       <c r="S24">
-        <v>-79</v>
+        <v>-31</v>
       </c>
       <c r="T24">
-        <v>-175</v>
+        <v>-333</v>
       </c>
       <c r="U24">
-        <v>-129</v>
+        <v>-266</v>
       </c>
       <c r="V24">
-        <v>226</v>
+        <v>36</v>
       </c>
       <c r="W24">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="X24">
-        <v>127</v>
+        <v>195</v>
       </c>
       <c r="Y24">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="Z24">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AA24">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AC24">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AD24">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AG24">
         <v>90</v>
       </c>
       <c r="AH24">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AI24">
         <v>180</v>
@@ -4986,132 +4986,137 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>old</t>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>-120</v>
+        <v>-36</v>
       </c>
       <c r="B25">
-        <v>-27</v>
+        <v>-268</v>
       </c>
       <c r="C25">
-        <v>-79</v>
+        <v>-183</v>
       </c>
       <c r="D25">
+        <v>-42</v>
+      </c>
+      <c r="E25">
+        <v>-264</v>
+      </c>
+      <c r="F25">
         <v>-180</v>
       </c>
-      <c r="E25">
-        <v>-29</v>
-      </c>
-      <c r="F25">
-        <v>-127</v>
-      </c>
       <c r="G25">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="H25">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="I25">
-        <v>180</v>
+        <v>337</v>
       </c>
       <c r="J25">
-        <v>175</v>
+        <v>334</v>
       </c>
       <c r="K25">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="L25">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="M25">
-        <v>-120</v>
+        <v>-33</v>
       </c>
       <c r="N25">
-        <v>-173</v>
+        <v>-110</v>
       </c>
       <c r="O25">
-        <v>-24</v>
+        <v>-257</v>
       </c>
       <c r="P25">
-        <v>129</v>
+        <v>336</v>
       </c>
       <c r="Q25">
-        <v>179</v>
+        <v>268</v>
       </c>
       <c r="R25">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="S25">
-        <v>-72</v>
+        <v>-261</v>
       </c>
       <c r="T25">
-        <v>-227</v>
+        <v>-115</v>
       </c>
       <c r="U25">
-        <v>-27</v>
+        <v>-187</v>
       </c>
       <c r="V25">
-        <v>76</v>
+        <v>257</v>
       </c>
       <c r="W25">
-        <v>227</v>
+        <v>112</v>
       </c>
       <c r="X25">
-        <v>173</v>
+        <v>44</v>
       </c>
       <c r="Y25">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="Z25">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AA25">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB25">
         <v>180</v>
       </c>
       <c r="AC25">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AD25">
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AG25">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AH25">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AI25">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AJ25">
         <v>270</v>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -5156,7 +5161,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -5170,26 +5175,21 @@
         </is>
       </c>
       <c r="AW25">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>new</t>
+          <t>old</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
     </row>

--- a/recog_phase.xlsx
+++ b/recog_phase.xlsx
@@ -623,88 +623,88 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>-258</v>
+        <v>-202</v>
       </c>
       <c r="B2">
-        <v>-195</v>
+        <v>-37</v>
       </c>
       <c r="C2">
-        <v>-340</v>
+        <v>-133</v>
       </c>
       <c r="D2">
-        <v>-111</v>
+        <v>-201</v>
       </c>
       <c r="E2">
-        <v>-259</v>
+        <v>-381</v>
       </c>
       <c r="F2">
-        <v>-43</v>
+        <v>-38</v>
       </c>
       <c r="G2">
-        <v>342</v>
+        <v>35</v>
       </c>
       <c r="H2">
+        <v>298</v>
+      </c>
+      <c r="I2">
+        <v>375</v>
+      </c>
+      <c r="J2">
+        <v>118</v>
+      </c>
+      <c r="K2">
+        <v>208</v>
+      </c>
+      <c r="L2">
+        <v>365</v>
+      </c>
+      <c r="M2">
+        <v>-129</v>
+      </c>
+      <c r="N2">
+        <v>-298</v>
+      </c>
+      <c r="O2">
+        <v>-210</v>
+      </c>
+      <c r="P2">
+        <v>205</v>
+      </c>
+      <c r="Q2">
+        <v>119</v>
+      </c>
+      <c r="R2">
         <v>41</v>
       </c>
-      <c r="I2">
-        <v>180</v>
-      </c>
-      <c r="J2">
-        <v>35</v>
-      </c>
-      <c r="K2">
-        <v>192</v>
-      </c>
-      <c r="L2">
-        <v>112</v>
-      </c>
-      <c r="M2">
-        <v>-32</v>
-      </c>
-      <c r="N2">
-        <v>-266</v>
-      </c>
-      <c r="O2">
-        <v>-194</v>
-      </c>
-      <c r="P2">
-        <v>116</v>
-      </c>
-      <c r="Q2">
-        <v>343</v>
-      </c>
-      <c r="R2">
-        <v>39</v>
-      </c>
       <c r="S2">
-        <v>-43</v>
+        <v>-295</v>
       </c>
       <c r="T2">
-        <v>-188</v>
+        <v>-125</v>
       </c>
       <c r="U2">
-        <v>-107</v>
+        <v>-374</v>
       </c>
       <c r="V2">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="W2">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="X2">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="Y2">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AA2">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AC2">
         <v>270</v>
@@ -713,22 +713,22 @@
         <v>180</v>
       </c>
       <c r="AE2">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AG2">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AI2">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -752,50 +752,50 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>L0.png</t>
         </is>
       </c>
       <c r="AW2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -816,112 +816,112 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>-34</v>
+        <v>-283</v>
       </c>
       <c r="B3">
-        <v>-182</v>
+        <v>-215</v>
       </c>
       <c r="C3">
-        <v>-112</v>
+        <v>-119</v>
       </c>
       <c r="D3">
-        <v>-259</v>
+        <v>-35</v>
       </c>
       <c r="E3">
-        <v>-338</v>
+        <v>-286</v>
       </c>
       <c r="F3">
-        <v>-41</v>
+        <v>-209</v>
       </c>
       <c r="G3">
-        <v>180</v>
+        <v>125</v>
       </c>
       <c r="H3">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="I3">
-        <v>263</v>
+        <v>376</v>
       </c>
       <c r="J3">
-        <v>258</v>
+        <v>44</v>
       </c>
       <c r="K3">
-        <v>340</v>
+        <v>199</v>
       </c>
       <c r="L3">
-        <v>31</v>
+        <v>290</v>
       </c>
       <c r="M3">
-        <v>-189</v>
+        <v>-202</v>
       </c>
       <c r="N3">
-        <v>-118</v>
+        <v>-48</v>
       </c>
       <c r="O3">
-        <v>-338</v>
+        <v>-289</v>
       </c>
       <c r="P3">
-        <v>258</v>
+        <v>367</v>
       </c>
       <c r="Q3">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="R3">
-        <v>193</v>
+        <v>125</v>
       </c>
       <c r="S3">
-        <v>-115</v>
+        <v>-380</v>
       </c>
       <c r="T3">
-        <v>-38</v>
+        <v>-298</v>
       </c>
       <c r="U3">
-        <v>-269</v>
+        <v>-124</v>
       </c>
       <c r="V3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="W3">
-        <v>192</v>
+        <v>292</v>
       </c>
       <c r="X3">
-        <v>334</v>
+        <v>124</v>
       </c>
       <c r="Y3">
         <v>180</v>
       </c>
       <c r="Z3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AC3">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AE3">
         <v>270</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AG3">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AH3">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AI3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -945,24 +945,24 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="AW3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1009,112 +1009,112 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>-31</v>
+        <v>-381</v>
       </c>
       <c r="B4">
-        <v>-342</v>
+        <v>-204</v>
       </c>
       <c r="C4">
-        <v>-117</v>
+        <v>-118</v>
       </c>
       <c r="D4">
-        <v>-260</v>
+        <v>-283</v>
       </c>
       <c r="E4">
-        <v>-187</v>
+        <v>-378</v>
       </c>
       <c r="F4">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H4">
-        <v>263</v>
+        <v>379</v>
       </c>
       <c r="I4">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="J4">
-        <v>259</v>
+        <v>204</v>
       </c>
       <c r="K4">
-        <v>120</v>
+        <v>297</v>
       </c>
       <c r="L4">
-        <v>41</v>
+        <v>366</v>
       </c>
       <c r="M4">
-        <v>-110</v>
+        <v>-42</v>
       </c>
       <c r="N4">
-        <v>-32</v>
+        <v>-213</v>
       </c>
       <c r="O4">
-        <v>-256</v>
+        <v>-373</v>
       </c>
       <c r="P4">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="Q4">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="R4">
-        <v>261</v>
+        <v>126</v>
       </c>
       <c r="S4">
-        <v>-343</v>
+        <v>-372</v>
       </c>
       <c r="T4">
-        <v>-116</v>
+        <v>-202</v>
       </c>
       <c r="U4">
-        <v>-258</v>
+        <v>-288</v>
       </c>
       <c r="V4">
-        <v>187</v>
+        <v>375</v>
       </c>
       <c r="W4">
-        <v>341</v>
+        <v>128</v>
       </c>
       <c r="X4">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="Y4">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AB4">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AD4">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF4">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AG4">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AI4">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AJ4">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1177,96 +1177,101 @@
         </is>
       </c>
       <c r="AW4">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
           <t>right</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>old</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>left</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>-334</v>
+        <v>-299</v>
       </c>
       <c r="B5">
-        <v>-118</v>
+        <v>-123</v>
       </c>
       <c r="C5">
-        <v>-193</v>
+        <v>-35</v>
       </c>
       <c r="D5">
-        <v>-334</v>
+        <v>-284</v>
       </c>
       <c r="E5">
-        <v>-257</v>
+        <v>-376</v>
       </c>
       <c r="F5">
-        <v>-184</v>
+        <v>-120</v>
       </c>
       <c r="G5">
-        <v>336</v>
+        <v>208</v>
       </c>
       <c r="H5">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="I5">
-        <v>259</v>
+        <v>37</v>
       </c>
       <c r="J5">
-        <v>266</v>
+        <v>204</v>
       </c>
       <c r="K5">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="L5">
-        <v>189</v>
+        <v>124</v>
       </c>
       <c r="M5">
-        <v>-108</v>
+        <v>-374</v>
       </c>
       <c r="N5">
-        <v>-192</v>
+        <v>-201</v>
       </c>
       <c r="O5">
-        <v>-270</v>
+        <v>-121</v>
       </c>
       <c r="P5">
-        <v>193</v>
+        <v>46</v>
       </c>
       <c r="Q5">
-        <v>113</v>
+        <v>292</v>
       </c>
       <c r="R5">
-        <v>334</v>
+        <v>116</v>
       </c>
       <c r="S5">
-        <v>-34</v>
+        <v>-203</v>
       </c>
       <c r="T5">
-        <v>-334</v>
+        <v>-121</v>
       </c>
       <c r="U5">
-        <v>-106</v>
+        <v>-38</v>
       </c>
       <c r="V5">
-        <v>185</v>
+        <v>41</v>
       </c>
       <c r="W5">
-        <v>334</v>
+        <v>376</v>
       </c>
       <c r="X5">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="Y5">
         <v>270</v>
@@ -1278,67 +1283,67 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AC5">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AD5">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AE5">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AF5">
         <v>90</v>
       </c>
       <c r="AG5">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ5">
         <v>0</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AR5" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -1365,102 +1370,107 @@
         </is>
       </c>
       <c r="AW5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
           <t>right</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>old</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>left</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>-39</v>
+        <v>-37</v>
       </c>
       <c r="B6">
-        <v>-186</v>
+        <v>-378</v>
       </c>
       <c r="C6">
-        <v>-115</v>
+        <v>-295</v>
       </c>
       <c r="D6">
-        <v>-111</v>
+        <v>-285</v>
       </c>
       <c r="E6">
-        <v>-258</v>
+        <v>-44</v>
       </c>
       <c r="F6">
-        <v>-343</v>
+        <v>-380</v>
       </c>
       <c r="G6">
-        <v>110</v>
+        <v>366</v>
       </c>
       <c r="H6">
-        <v>338</v>
+        <v>120</v>
       </c>
       <c r="I6">
-        <v>187</v>
+        <v>40</v>
       </c>
       <c r="J6">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="K6">
-        <v>118</v>
+        <v>287</v>
       </c>
       <c r="L6">
+        <v>130</v>
+      </c>
+      <c r="M6">
+        <v>-117</v>
+      </c>
+      <c r="N6">
+        <v>-371</v>
+      </c>
+      <c r="O6">
+        <v>-294</v>
+      </c>
+      <c r="P6">
+        <v>297</v>
+      </c>
+      <c r="Q6">
+        <v>202</v>
+      </c>
+      <c r="R6">
         <v>37</v>
       </c>
-      <c r="M6">
-        <v>-333</v>
-      </c>
-      <c r="N6">
-        <v>-256</v>
-      </c>
-      <c r="O6">
-        <v>-193</v>
-      </c>
-      <c r="P6">
-        <v>109</v>
-      </c>
-      <c r="Q6">
-        <v>264</v>
-      </c>
-      <c r="R6">
-        <v>39</v>
-      </c>
       <c r="S6">
-        <v>-110</v>
+        <v>-48</v>
       </c>
       <c r="T6">
-        <v>-183</v>
+        <v>-378</v>
       </c>
       <c r="U6">
-        <v>-340</v>
+        <v>-213</v>
       </c>
       <c r="V6">
-        <v>258</v>
+        <v>130</v>
       </c>
       <c r="W6">
-        <v>37</v>
+        <v>294</v>
       </c>
       <c r="X6">
-        <v>195</v>
+        <v>372</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Z6">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AA6">
         <v>180</v>
@@ -1469,28 +1479,28 @@
         <v>0</v>
       </c>
       <c r="AC6">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AE6">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AF6">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AG6">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AH6">
         <v>90</v>
       </c>
       <c r="AI6">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
@@ -1534,7 +1544,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
@@ -1544,7 +1554,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1553,7 +1563,7 @@
         </is>
       </c>
       <c r="AW6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1562,123 +1572,128 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>old</t>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>-106</v>
+        <v>-288</v>
       </c>
       <c r="B7">
-        <v>-344</v>
+        <v>-212</v>
       </c>
       <c r="C7">
-        <v>-189</v>
+        <v>-379</v>
       </c>
       <c r="D7">
-        <v>-109</v>
+        <v>-48</v>
       </c>
       <c r="E7">
-        <v>-330</v>
+        <v>-127</v>
       </c>
       <c r="F7">
-        <v>-257</v>
+        <v>-378</v>
       </c>
       <c r="G7">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H7">
-        <v>117</v>
+        <v>211</v>
       </c>
       <c r="I7">
-        <v>257</v>
+        <v>126</v>
       </c>
       <c r="J7">
-        <v>268</v>
+        <v>200</v>
       </c>
       <c r="K7">
-        <v>43</v>
+        <v>295</v>
       </c>
       <c r="L7">
-        <v>183</v>
+        <v>38</v>
       </c>
       <c r="M7">
-        <v>-30</v>
+        <v>-38</v>
       </c>
       <c r="N7">
-        <v>-186</v>
+        <v>-368</v>
       </c>
       <c r="O7">
-        <v>-266</v>
+        <v>-127</v>
       </c>
       <c r="P7">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="Q7">
-        <v>41</v>
+        <v>202</v>
       </c>
       <c r="R7">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="S7">
-        <v>-194</v>
+        <v>-129</v>
       </c>
       <c r="T7">
-        <v>-44</v>
+        <v>-369</v>
       </c>
       <c r="U7">
-        <v>-117</v>
+        <v>-40</v>
       </c>
       <c r="V7">
-        <v>31</v>
+        <v>372</v>
       </c>
       <c r="W7">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="X7">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="Y7">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AA7">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AB7">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AC7">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AD7">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AF7">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AG7">
         <v>270</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AI7">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AJ7">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
@@ -1712,7 +1727,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1732,7 +1747,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1741,7 +1756,7 @@
         </is>
       </c>
       <c r="AW7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1761,112 +1776,112 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>-269</v>
+        <v>-44</v>
       </c>
       <c r="B8">
-        <v>-38</v>
+        <v>-296</v>
       </c>
       <c r="C8">
-        <v>-115</v>
+        <v>-212</v>
       </c>
       <c r="D8">
-        <v>-268</v>
+        <v>-212</v>
       </c>
       <c r="E8">
-        <v>-31</v>
+        <v>-46</v>
       </c>
       <c r="F8">
-        <v>-116</v>
+        <v>-119</v>
       </c>
       <c r="G8">
-        <v>180</v>
+        <v>49</v>
       </c>
       <c r="H8">
-        <v>33</v>
+        <v>287</v>
       </c>
       <c r="I8">
-        <v>263</v>
+        <v>125</v>
       </c>
       <c r="J8">
-        <v>270</v>
+        <v>44</v>
       </c>
       <c r="K8">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="L8">
-        <v>336</v>
+        <v>203</v>
       </c>
       <c r="M8">
-        <v>-186</v>
+        <v>-368</v>
       </c>
       <c r="N8">
-        <v>-34</v>
+        <v>-47</v>
       </c>
       <c r="O8">
-        <v>-344</v>
+        <v>-202</v>
       </c>
       <c r="P8">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="Q8">
-        <v>32</v>
+        <v>366</v>
       </c>
       <c r="R8">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="S8">
-        <v>-339</v>
+        <v>-118</v>
       </c>
       <c r="T8">
-        <v>-36</v>
+        <v>-297</v>
       </c>
       <c r="U8">
-        <v>-256</v>
+        <v>-42</v>
       </c>
       <c r="V8">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="W8">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="X8">
-        <v>331</v>
+        <v>211</v>
       </c>
       <c r="Y8">
         <v>90</v>
       </c>
       <c r="Z8">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AA8">
         <v>180</v>
       </c>
       <c r="AB8">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AD8">
         <v>0</v>
       </c>
       <c r="AE8">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AG8">
         <v>270</v>
       </c>
       <c r="AH8">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ8">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
@@ -1910,12 +1925,12 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -1929,11 +1944,11 @@
         </is>
       </c>
       <c r="AW8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1949,116 +1964,116 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>-41</v>
+        <v>-39</v>
       </c>
       <c r="B9">
         <v>-117</v>
       </c>
       <c r="C9">
-        <v>-190</v>
+        <v>-368</v>
       </c>
       <c r="D9">
-        <v>-332</v>
+        <v>-42</v>
       </c>
       <c r="E9">
-        <v>-108</v>
+        <v>-127</v>
       </c>
       <c r="F9">
-        <v>-267</v>
+        <v>-201</v>
       </c>
       <c r="G9">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="H9">
-        <v>36</v>
+        <v>380</v>
       </c>
       <c r="I9">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J9">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="K9">
-        <v>335</v>
+        <v>127</v>
       </c>
       <c r="L9">
-        <v>181</v>
+        <v>380</v>
       </c>
       <c r="M9">
-        <v>-259</v>
+        <v>-295</v>
       </c>
       <c r="N9">
-        <v>-37</v>
+        <v>-207</v>
       </c>
       <c r="O9">
-        <v>-341</v>
+        <v>-122</v>
       </c>
       <c r="P9">
-        <v>338</v>
+        <v>42</v>
       </c>
       <c r="Q9">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="R9">
-        <v>34</v>
+        <v>372</v>
       </c>
       <c r="S9">
-        <v>-337</v>
+        <v>-368</v>
       </c>
       <c r="T9">
-        <v>-31</v>
+        <v>-288</v>
       </c>
       <c r="U9">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="V9">
-        <v>336</v>
+        <v>288</v>
       </c>
       <c r="W9">
-        <v>189</v>
+        <v>367</v>
       </c>
       <c r="X9">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Y9">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="Z9">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AB9">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AC9">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AD9">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AG9">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AI9">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2113,11 +2128,11 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW9">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2126,191 +2141,186 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>new</t>
+          <t>old</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>-36</v>
+        <v>-373</v>
       </c>
       <c r="B10">
-        <v>-344</v>
+        <v>-203</v>
       </c>
       <c r="C10">
-        <v>-110</v>
+        <v>-133</v>
       </c>
       <c r="D10">
-        <v>-334</v>
+        <v>-289</v>
       </c>
       <c r="E10">
-        <v>-186</v>
+        <v>-206</v>
       </c>
       <c r="F10">
-        <v>-107</v>
+        <v>-130</v>
       </c>
       <c r="G10">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="H10">
-        <v>187</v>
+        <v>122</v>
       </c>
       <c r="I10">
-        <v>267</v>
+        <v>374</v>
       </c>
       <c r="J10">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="K10">
-        <v>108</v>
+        <v>203</v>
       </c>
       <c r="L10">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M10">
-        <v>-257</v>
+        <v>-284</v>
       </c>
       <c r="N10">
-        <v>-42</v>
+        <v>-130</v>
       </c>
       <c r="O10">
-        <v>-193</v>
+        <v>-39</v>
       </c>
       <c r="P10">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q10">
-        <v>331</v>
+        <v>210</v>
       </c>
       <c r="R10">
         <v>117</v>
       </c>
       <c r="S10">
-        <v>-42</v>
+        <v>-205</v>
       </c>
       <c r="T10">
-        <v>-338</v>
+        <v>-35</v>
       </c>
       <c r="U10">
-        <v>-191</v>
+        <v>-124</v>
       </c>
       <c r="V10">
-        <v>44</v>
+        <v>214</v>
       </c>
       <c r="W10">
-        <v>185</v>
+        <v>121</v>
       </c>
       <c r="X10">
-        <v>119</v>
+        <v>295</v>
       </c>
       <c r="Y10">
         <v>90</v>
       </c>
       <c r="Z10">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AA10">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AB10">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AC10">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AF10">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AG10">
         <v>180</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AW10">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2335,85 +2345,85 @@
     </row>
     <row r="11">
       <c r="A11">
+        <v>-295</v>
+      </c>
+      <c r="B11">
+        <v>-121</v>
+      </c>
+      <c r="C11">
+        <v>-36</v>
+      </c>
+      <c r="D11">
+        <v>-34</v>
+      </c>
+      <c r="E11">
+        <v>-214</v>
+      </c>
+      <c r="F11">
+        <v>-290</v>
+      </c>
+      <c r="G11">
+        <v>381</v>
+      </c>
+      <c r="H11">
+        <v>208</v>
+      </c>
+      <c r="I11">
+        <v>119</v>
+      </c>
+      <c r="J11">
+        <v>381</v>
+      </c>
+      <c r="K11">
+        <v>40</v>
+      </c>
+      <c r="L11">
+        <v>295</v>
+      </c>
+      <c r="M11">
         <v>-38</v>
       </c>
-      <c r="B11">
-        <v>-341</v>
-      </c>
-      <c r="C11">
-        <v>-186</v>
-      </c>
-      <c r="D11">
-        <v>-40</v>
-      </c>
-      <c r="E11">
-        <v>-114</v>
-      </c>
-      <c r="F11">
-        <v>-343</v>
-      </c>
-      <c r="G11">
-        <v>108</v>
-      </c>
-      <c r="H11">
-        <v>34</v>
-      </c>
-      <c r="I11">
-        <v>338</v>
-      </c>
-      <c r="J11">
-        <v>182</v>
-      </c>
-      <c r="K11">
-        <v>36</v>
-      </c>
-      <c r="L11">
-        <v>117</v>
-      </c>
-      <c r="M11">
-        <v>-31</v>
-      </c>
       <c r="N11">
-        <v>-113</v>
+        <v>-284</v>
       </c>
       <c r="O11">
-        <v>-257</v>
+        <v>-118</v>
       </c>
       <c r="P11">
-        <v>339</v>
+        <v>295</v>
       </c>
       <c r="Q11">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="R11">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="S11">
-        <v>-336</v>
+        <v>-36</v>
       </c>
       <c r="T11">
-        <v>-40</v>
+        <v>-372</v>
       </c>
       <c r="U11">
-        <v>-108</v>
+        <v>-209</v>
       </c>
       <c r="V11">
-        <v>194</v>
+        <v>376</v>
       </c>
       <c r="W11">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="X11">
-        <v>39</v>
+        <v>291</v>
       </c>
       <c r="Y11">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="Z11">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AB11">
         <v>0</v>
@@ -2422,25 +2432,25 @@
         <v>90</v>
       </c>
       <c r="AD11">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AF11">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AG11">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AH11">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ11">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
@@ -2479,14 +2489,14 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -2503,116 +2513,111 @@
         </is>
       </c>
       <c r="AW11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>new</t>
+          <t>old</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>-191</v>
+        <v>-367</v>
       </c>
       <c r="B12">
-        <v>-108</v>
+        <v>-207</v>
       </c>
       <c r="C12">
-        <v>-344</v>
+        <v>-118</v>
       </c>
       <c r="D12">
-        <v>-265</v>
+        <v>-205</v>
       </c>
       <c r="E12">
-        <v>-118</v>
+        <v>-45</v>
       </c>
       <c r="F12">
-        <v>-44</v>
+        <v>-379</v>
       </c>
       <c r="G12">
-        <v>118</v>
+        <v>371</v>
       </c>
       <c r="H12">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I12">
-        <v>340</v>
+        <v>204</v>
       </c>
       <c r="J12">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="K12">
-        <v>343</v>
+        <v>292</v>
       </c>
       <c r="L12">
-        <v>43</v>
+        <v>381</v>
       </c>
       <c r="M12">
-        <v>-344</v>
+        <v>-286</v>
       </c>
       <c r="N12">
-        <v>-37</v>
+        <v>-369</v>
       </c>
       <c r="O12">
-        <v>-269</v>
+        <v>-35</v>
       </c>
       <c r="P12">
-        <v>262</v>
+        <v>374</v>
       </c>
       <c r="Q12">
-        <v>188</v>
+        <v>47</v>
       </c>
       <c r="R12">
-        <v>107</v>
+        <v>298</v>
       </c>
       <c r="S12">
-        <v>-112</v>
+        <v>-374</v>
       </c>
       <c r="T12">
-        <v>-267</v>
+        <v>-287</v>
       </c>
       <c r="U12">
-        <v>-187</v>
+        <v>-121</v>
       </c>
       <c r="V12">
-        <v>266</v>
+        <v>36</v>
       </c>
       <c r="W12">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="X12">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="Y12">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="Z12">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AA12">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AD12">
         <v>270</v>
@@ -2621,19 +2626,19 @@
         <v>180</v>
       </c>
       <c r="AF12">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AH12">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AI12">
         <v>90</v>
       </c>
       <c r="AJ12">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
@@ -2642,7 +2647,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -2662,7 +2667,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2696,7 +2701,7 @@
         </is>
       </c>
       <c r="AW12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
@@ -2705,87 +2710,92 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>old</t>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>-111</v>
+        <v>-380</v>
       </c>
       <c r="B13">
-        <v>-269</v>
+        <v>-121</v>
       </c>
       <c r="C13">
-        <v>-331</v>
+        <v>-215</v>
       </c>
       <c r="D13">
-        <v>-40</v>
+        <v>-45</v>
       </c>
       <c r="E13">
-        <v>-118</v>
+        <v>-282</v>
       </c>
       <c r="F13">
-        <v>-263</v>
+        <v>-380</v>
       </c>
       <c r="G13">
-        <v>188</v>
+        <v>33</v>
       </c>
       <c r="H13">
-        <v>345</v>
+        <v>372</v>
       </c>
       <c r="I13">
-        <v>268</v>
+        <v>124</v>
       </c>
       <c r="J13">
-        <v>341</v>
+        <v>292</v>
       </c>
       <c r="K13">
-        <v>44</v>
+        <v>376</v>
       </c>
       <c r="L13">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="M13">
-        <v>-111</v>
+        <v>-370</v>
       </c>
       <c r="N13">
-        <v>-264</v>
+        <v>-210</v>
       </c>
       <c r="O13">
-        <v>-31</v>
+        <v>-38</v>
       </c>
       <c r="P13">
-        <v>34</v>
+        <v>380</v>
       </c>
       <c r="Q13">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="R13">
-        <v>336</v>
+        <v>288</v>
       </c>
       <c r="S13">
-        <v>-195</v>
+        <v>-36</v>
       </c>
       <c r="T13">
-        <v>-335</v>
+        <v>-126</v>
       </c>
       <c r="U13">
-        <v>-37</v>
+        <v>-369</v>
       </c>
       <c r="V13">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="W13">
-        <v>117</v>
+        <v>372</v>
       </c>
       <c r="X13">
-        <v>182</v>
+        <v>42</v>
       </c>
       <c r="Y13">
         <v>90</v>
@@ -2794,34 +2804,34 @@
         <v>270</v>
       </c>
       <c r="AA13">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AC13">
         <v>90</v>
       </c>
       <c r="AD13">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AE13">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AH13">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
@@ -2830,7 +2840,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2840,7 +2850,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2884,7 +2894,7 @@
         </is>
       </c>
       <c r="AW13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
@@ -2893,111 +2903,116 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>old</t>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>-110</v>
+        <v>-116</v>
       </c>
       <c r="B14">
+        <v>-39</v>
+      </c>
+      <c r="C14">
+        <v>-206</v>
+      </c>
+      <c r="D14">
+        <v>-125</v>
+      </c>
+      <c r="E14">
+        <v>-294</v>
+      </c>
+      <c r="F14">
+        <v>-46</v>
+      </c>
+      <c r="G14">
+        <v>285</v>
+      </c>
+      <c r="H14">
+        <v>204</v>
+      </c>
+      <c r="I14">
+        <v>376</v>
+      </c>
+      <c r="J14">
+        <v>378</v>
+      </c>
+      <c r="K14">
+        <v>43</v>
+      </c>
+      <c r="L14">
+        <v>289</v>
+      </c>
+      <c r="M14">
+        <v>-294</v>
+      </c>
+      <c r="N14">
+        <v>-34</v>
+      </c>
+      <c r="O14">
+        <v>-368</v>
+      </c>
+      <c r="P14">
+        <v>33</v>
+      </c>
+      <c r="Q14">
+        <v>209</v>
+      </c>
+      <c r="R14">
+        <v>117</v>
+      </c>
+      <c r="S14">
         <v>-41</v>
       </c>
-      <c r="C14">
-        <v>-185</v>
-      </c>
-      <c r="D14">
-        <v>-106</v>
-      </c>
-      <c r="E14">
-        <v>-32</v>
-      </c>
-      <c r="F14">
-        <v>-259</v>
-      </c>
-      <c r="G14">
-        <v>115</v>
-      </c>
-      <c r="H14">
-        <v>259</v>
-      </c>
-      <c r="I14">
-        <v>192</v>
-      </c>
-      <c r="J14">
-        <v>182</v>
-      </c>
-      <c r="K14">
-        <v>262</v>
-      </c>
-      <c r="L14">
-        <v>333</v>
-      </c>
-      <c r="M14">
-        <v>-181</v>
-      </c>
-      <c r="N14">
-        <v>-344</v>
-      </c>
-      <c r="O14">
-        <v>-108</v>
-      </c>
-      <c r="P14">
-        <v>259</v>
-      </c>
-      <c r="Q14">
-        <v>37</v>
-      </c>
-      <c r="R14">
-        <v>116</v>
-      </c>
-      <c r="S14">
-        <v>-184</v>
-      </c>
       <c r="T14">
-        <v>-263</v>
+        <v>-213</v>
       </c>
       <c r="U14">
-        <v>-44</v>
+        <v>-286</v>
       </c>
       <c r="V14">
-        <v>260</v>
+        <v>127</v>
       </c>
       <c r="W14">
-        <v>117</v>
+        <v>205</v>
       </c>
       <c r="X14">
-        <v>191</v>
+        <v>292</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Z14">
         <v>90</v>
       </c>
       <c r="AA14">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AC14">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AD14">
         <v>180</v>
       </c>
       <c r="AE14">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AG14">
         <v>270</v>
@@ -3006,7 +3021,7 @@
         <v>180</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AJ14">
         <v>0</v>
@@ -3053,26 +3068,26 @@
       </c>
       <c r="AS14" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>L0.png</t>
         </is>
       </c>
       <c r="AW14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
@@ -3081,128 +3096,123 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>new</t>
+          <t>old</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>-185</v>
+        <v>-121</v>
       </c>
       <c r="B15">
-        <v>-43</v>
+        <v>-209</v>
       </c>
       <c r="C15">
-        <v>-334</v>
+        <v>-376</v>
       </c>
       <c r="D15">
-        <v>-39</v>
+        <v>-119</v>
       </c>
       <c r="E15">
-        <v>-266</v>
+        <v>-45</v>
       </c>
       <c r="F15">
-        <v>-181</v>
+        <v>-288</v>
       </c>
       <c r="G15">
-        <v>181</v>
+        <v>36</v>
       </c>
       <c r="H15">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="I15">
-        <v>262</v>
+        <v>213</v>
       </c>
       <c r="J15">
-        <v>340</v>
+        <v>43</v>
       </c>
       <c r="K15">
+        <v>121</v>
+      </c>
+      <c r="L15">
+        <v>382</v>
+      </c>
+      <c r="M15">
+        <v>-373</v>
+      </c>
+      <c r="N15">
+        <v>-124</v>
+      </c>
+      <c r="O15">
+        <v>-209</v>
+      </c>
+      <c r="P15">
+        <v>202</v>
+      </c>
+      <c r="Q15">
+        <v>125</v>
+      </c>
+      <c r="R15">
         <v>44</v>
       </c>
-      <c r="L15">
-        <v>260</v>
-      </c>
-      <c r="M15">
-        <v>-185</v>
-      </c>
-      <c r="N15">
-        <v>-41</v>
-      </c>
-      <c r="O15">
-        <v>-115</v>
-      </c>
-      <c r="P15">
-        <v>31</v>
-      </c>
-      <c r="Q15">
-        <v>334</v>
-      </c>
-      <c r="R15">
-        <v>116</v>
-      </c>
       <c r="S15">
-        <v>-117</v>
+        <v>-283</v>
       </c>
       <c r="T15">
-        <v>-43</v>
+        <v>-125</v>
       </c>
       <c r="U15">
-        <v>-334</v>
+        <v>-209</v>
       </c>
       <c r="V15">
-        <v>44</v>
+        <v>284</v>
       </c>
       <c r="W15">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="X15">
-        <v>106</v>
+        <v>376</v>
       </c>
       <c r="Y15">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="Z15">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AB15">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AC15">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AE15">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AG15">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AI15">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
@@ -3226,29 +3236,29 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AT15" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -3265,132 +3275,137 @@
         </is>
       </c>
       <c r="AW15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
           <t>right</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>old</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>left</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>-34</v>
+        <v>-207</v>
       </c>
       <c r="B16">
-        <v>-113</v>
+        <v>-296</v>
       </c>
       <c r="C16">
-        <v>-261</v>
+        <v>-41</v>
       </c>
       <c r="D16">
-        <v>-190</v>
+        <v>-299</v>
       </c>
       <c r="E16">
-        <v>-336</v>
+        <v>-43</v>
       </c>
       <c r="F16">
-        <v>-115</v>
+        <v>-126</v>
       </c>
       <c r="G16">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="H16">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="I16">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="J16">
-        <v>262</v>
+        <v>36</v>
       </c>
       <c r="K16">
-        <v>195</v>
+        <v>288</v>
       </c>
       <c r="L16">
+        <v>211</v>
+      </c>
+      <c r="M16">
+        <v>-214</v>
+      </c>
+      <c r="N16">
+        <v>-286</v>
+      </c>
+      <c r="O16">
+        <v>-41</v>
+      </c>
+      <c r="P16">
+        <v>290</v>
+      </c>
+      <c r="Q16">
+        <v>374</v>
+      </c>
+      <c r="R16">
+        <v>131</v>
+      </c>
+      <c r="S16">
+        <v>-37</v>
+      </c>
+      <c r="T16">
+        <v>-295</v>
+      </c>
+      <c r="U16">
+        <v>-216</v>
+      </c>
+      <c r="V16">
         <v>44</v>
       </c>
-      <c r="M16">
-        <v>-38</v>
-      </c>
-      <c r="N16">
-        <v>-340</v>
-      </c>
-      <c r="O16">
-        <v>-191</v>
-      </c>
-      <c r="P16">
-        <v>337</v>
-      </c>
-      <c r="Q16">
-        <v>262</v>
-      </c>
-      <c r="R16">
-        <v>35</v>
-      </c>
-      <c r="S16">
-        <v>-336</v>
-      </c>
-      <c r="T16">
-        <v>-260</v>
-      </c>
-      <c r="U16">
-        <v>-120</v>
-      </c>
-      <c r="V16">
-        <v>41</v>
-      </c>
       <c r="W16">
-        <v>188</v>
+        <v>116</v>
       </c>
       <c r="X16">
-        <v>117</v>
+        <v>370</v>
       </c>
       <c r="Y16">
         <v>90</v>
       </c>
       <c r="Z16">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AB16">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AD16">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AG16">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AI16">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AJ16">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
@@ -3409,29 +3424,29 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -3453,7 +3468,7 @@
         </is>
       </c>
       <c r="AW16">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
@@ -3462,101 +3477,96 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>new</t>
+          <t>old</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>-118</v>
+        <v>-44</v>
       </c>
       <c r="B17">
-        <v>-265</v>
+        <v>-379</v>
       </c>
       <c r="C17">
-        <v>-334</v>
+        <v>-284</v>
       </c>
       <c r="D17">
-        <v>-262</v>
+        <v>-131</v>
       </c>
       <c r="E17">
-        <v>-340</v>
+        <v>-213</v>
       </c>
       <c r="F17">
-        <v>-184</v>
+        <v>-43</v>
       </c>
       <c r="G17">
-        <v>36</v>
+        <v>288</v>
       </c>
       <c r="H17">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="I17">
-        <v>261</v>
+        <v>117</v>
       </c>
       <c r="J17">
-        <v>263</v>
+        <v>38</v>
       </c>
       <c r="K17">
+        <v>128</v>
+      </c>
+      <c r="L17">
+        <v>212</v>
+      </c>
+      <c r="M17">
+        <v>-131</v>
+      </c>
+      <c r="N17">
+        <v>-381</v>
+      </c>
+      <c r="O17">
+        <v>-292</v>
+      </c>
+      <c r="P17">
+        <v>201</v>
+      </c>
+      <c r="Q17">
+        <v>130</v>
+      </c>
+      <c r="R17">
         <v>41</v>
       </c>
-      <c r="L17">
-        <v>184</v>
-      </c>
-      <c r="M17">
-        <v>-42</v>
-      </c>
-      <c r="N17">
-        <v>-258</v>
-      </c>
-      <c r="O17">
-        <v>-184</v>
-      </c>
-      <c r="P17">
-        <v>34</v>
-      </c>
-      <c r="Q17">
-        <v>110</v>
-      </c>
-      <c r="R17">
-        <v>267</v>
-      </c>
       <c r="S17">
-        <v>-180</v>
+        <v>-133</v>
       </c>
       <c r="T17">
-        <v>-116</v>
+        <v>-214</v>
       </c>
       <c r="U17">
-        <v>-332</v>
+        <v>-375</v>
       </c>
       <c r="V17">
-        <v>117</v>
+        <v>214</v>
       </c>
       <c r="W17">
-        <v>262</v>
+        <v>125</v>
       </c>
       <c r="X17">
-        <v>331</v>
+        <v>370</v>
       </c>
       <c r="Y17">
         <v>180</v>
       </c>
       <c r="Z17">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AB17">
         <v>270</v>
@@ -3565,25 +3575,25 @@
         <v>270</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AH17">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AJ17">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
@@ -3602,19 +3612,19 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AQ17" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -3646,11 +3656,11 @@
         </is>
       </c>
       <c r="AW17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -3666,112 +3676,112 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>-33</v>
+        <v>-295</v>
       </c>
       <c r="B18">
-        <v>-194</v>
+        <v>-46</v>
       </c>
       <c r="C18">
-        <v>-108</v>
+        <v>-202</v>
       </c>
       <c r="D18">
-        <v>-260</v>
+        <v>-209</v>
       </c>
       <c r="E18">
-        <v>-40</v>
+        <v>-117</v>
       </c>
       <c r="F18">
-        <v>-336</v>
+        <v>-372</v>
       </c>
       <c r="G18">
-        <v>107</v>
+        <v>203</v>
       </c>
       <c r="H18">
-        <v>344</v>
+        <v>285</v>
       </c>
       <c r="I18">
-        <v>182</v>
+        <v>127</v>
       </c>
       <c r="J18">
-        <v>336</v>
+        <v>117</v>
       </c>
       <c r="K18">
-        <v>188</v>
+        <v>287</v>
       </c>
       <c r="L18">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="M18">
-        <v>-344</v>
+        <v>-296</v>
       </c>
       <c r="N18">
-        <v>-113</v>
+        <v>-200</v>
       </c>
       <c r="O18">
-        <v>-263</v>
+        <v>-42</v>
       </c>
       <c r="P18">
-        <v>260</v>
+        <v>36</v>
       </c>
       <c r="Q18">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="R18">
-        <v>180</v>
+        <v>291</v>
       </c>
       <c r="S18">
-        <v>-33</v>
+        <v>-202</v>
       </c>
       <c r="T18">
-        <v>-260</v>
+        <v>-120</v>
       </c>
       <c r="U18">
-        <v>-185</v>
+        <v>-376</v>
       </c>
       <c r="V18">
-        <v>344</v>
+        <v>129</v>
       </c>
       <c r="W18">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="X18">
-        <v>33</v>
+        <v>374</v>
       </c>
       <c r="Y18">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="Z18">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AB18">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AD18">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AE18">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AG18">
         <v>90</v>
       </c>
       <c r="AH18">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
@@ -3838,7 +3848,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -3859,112 +3869,112 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>-267</v>
+        <v>-378</v>
       </c>
       <c r="B19">
-        <v>-115</v>
+        <v>-129</v>
       </c>
       <c r="C19">
-        <v>-339</v>
+        <v>-213</v>
       </c>
       <c r="D19">
-        <v>-333</v>
+        <v>-214</v>
       </c>
       <c r="E19">
-        <v>-189</v>
+        <v>-37</v>
       </c>
       <c r="F19">
-        <v>-108</v>
+        <v>-378</v>
       </c>
       <c r="G19">
-        <v>257</v>
+        <v>210</v>
       </c>
       <c r="H19">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I19">
-        <v>192</v>
+        <v>48</v>
       </c>
       <c r="J19">
-        <v>342</v>
+        <v>128</v>
       </c>
       <c r="K19">
-        <v>39</v>
+        <v>298</v>
       </c>
       <c r="L19">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="M19">
-        <v>-266</v>
+        <v>-118</v>
       </c>
       <c r="N19">
-        <v>-343</v>
+        <v>-293</v>
       </c>
       <c r="O19">
-        <v>-110</v>
+        <v>-45</v>
       </c>
       <c r="P19">
-        <v>259</v>
+        <v>117</v>
       </c>
       <c r="Q19">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="R19">
-        <v>183</v>
+        <v>287</v>
       </c>
       <c r="S19">
-        <v>-39</v>
+        <v>-47</v>
       </c>
       <c r="T19">
-        <v>-262</v>
+        <v>-289</v>
       </c>
       <c r="U19">
-        <v>-119</v>
+        <v>-117</v>
       </c>
       <c r="V19">
-        <v>333</v>
+        <v>208</v>
       </c>
       <c r="W19">
-        <v>266</v>
+        <v>45</v>
       </c>
       <c r="X19">
-        <v>43</v>
+        <v>288</v>
       </c>
       <c r="Y19">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AA19">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AB19">
         <v>270</v>
       </c>
       <c r="AC19">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AD19">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AH19">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AI19">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AJ19">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
@@ -4008,12 +4018,12 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -4027,7 +4037,7 @@
         </is>
       </c>
       <c r="AW19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
@@ -4036,99 +4046,104 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>old</t>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>-261</v>
+        <v>-37</v>
       </c>
       <c r="B20">
-        <v>-182</v>
+        <v>-121</v>
       </c>
       <c r="C20">
-        <v>-40</v>
+        <v>-285</v>
       </c>
       <c r="D20">
-        <v>-109</v>
+        <v>-214</v>
       </c>
       <c r="E20">
-        <v>-267</v>
+        <v>-376</v>
       </c>
       <c r="F20">
-        <v>-35</v>
+        <v>-120</v>
       </c>
       <c r="G20">
-        <v>344</v>
+        <v>43</v>
       </c>
       <c r="H20">
-        <v>45</v>
+        <v>204</v>
       </c>
       <c r="I20">
-        <v>195</v>
+        <v>298</v>
       </c>
       <c r="J20">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="K20">
-        <v>32</v>
+        <v>296</v>
       </c>
       <c r="L20">
-        <v>259</v>
+        <v>36</v>
       </c>
       <c r="M20">
-        <v>-260</v>
+        <v>-205</v>
       </c>
       <c r="N20">
-        <v>-31</v>
+        <v>-125</v>
       </c>
       <c r="O20">
-        <v>-106</v>
+        <v>-286</v>
       </c>
       <c r="P20">
-        <v>270</v>
+        <v>130</v>
       </c>
       <c r="Q20">
-        <v>331</v>
+        <v>380</v>
       </c>
       <c r="R20">
-        <v>36</v>
+        <v>202</v>
       </c>
       <c r="S20">
-        <v>-31</v>
+        <v>-124</v>
       </c>
       <c r="T20">
-        <v>-342</v>
+        <v>-366</v>
       </c>
       <c r="U20">
-        <v>-269</v>
+        <v>-45</v>
       </c>
       <c r="V20">
-        <v>180</v>
+        <v>298</v>
       </c>
       <c r="W20">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="X20">
-        <v>32</v>
+        <v>369</v>
       </c>
       <c r="Y20">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AA20">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -4137,22 +4152,22 @@
         <v>180</v>
       </c>
       <c r="AE20">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AF20">
         <v>270</v>
       </c>
       <c r="AG20">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AH20">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ20">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
@@ -4191,7 +4206,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -4211,11 +4226,11 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW20">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
@@ -4224,128 +4239,123 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>new</t>
+          <t>old</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>-341</v>
+        <v>-287</v>
       </c>
       <c r="B21">
-        <v>-183</v>
+        <v>-203</v>
       </c>
       <c r="C21">
-        <v>-38</v>
+        <v>-127</v>
       </c>
       <c r="D21">
-        <v>-185</v>
+        <v>-123</v>
       </c>
       <c r="E21">
-        <v>-333</v>
+        <v>-205</v>
       </c>
       <c r="F21">
-        <v>-114</v>
+        <v>-283</v>
       </c>
       <c r="G21">
-        <v>112</v>
+        <v>296</v>
       </c>
       <c r="H21">
-        <v>187</v>
+        <v>120</v>
       </c>
       <c r="I21">
-        <v>332</v>
+        <v>42</v>
       </c>
       <c r="J21">
-        <v>331</v>
+        <v>124</v>
       </c>
       <c r="K21">
-        <v>260</v>
+        <v>373</v>
       </c>
       <c r="L21">
-        <v>31</v>
+        <v>296</v>
       </c>
       <c r="M21">
-        <v>-344</v>
+        <v>-288</v>
       </c>
       <c r="N21">
-        <v>-116</v>
+        <v>-129</v>
       </c>
       <c r="O21">
-        <v>-31</v>
+        <v>-206</v>
       </c>
       <c r="P21">
-        <v>116</v>
+        <v>283</v>
       </c>
       <c r="Q21">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="R21">
-        <v>258</v>
+        <v>366</v>
       </c>
       <c r="S21">
-        <v>-339</v>
+        <v>-49</v>
       </c>
       <c r="T21">
-        <v>-34</v>
+        <v>-200</v>
       </c>
       <c r="U21">
-        <v>-119</v>
+        <v>-288</v>
       </c>
       <c r="V21">
-        <v>118</v>
+        <v>376</v>
       </c>
       <c r="W21">
-        <v>39</v>
+        <v>287</v>
       </c>
       <c r="X21">
-        <v>258</v>
+        <v>44</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="Z21">
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AB21">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AC21">
         <v>270</v>
       </c>
       <c r="AD21">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AE21">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AF21">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AG21">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AI21">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AJ21">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
@@ -4417,149 +4427,144 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>new</t>
+          <t>old</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>-267</v>
+        <v>-43</v>
       </c>
       <c r="B22">
-        <v>-108</v>
+        <v>-381</v>
       </c>
       <c r="C22">
-        <v>-32</v>
+        <v>-119</v>
       </c>
       <c r="D22">
-        <v>-40</v>
+        <v>-292</v>
       </c>
       <c r="E22">
-        <v>-181</v>
+        <v>-42</v>
       </c>
       <c r="F22">
-        <v>-113</v>
+        <v>-131</v>
       </c>
       <c r="G22">
-        <v>35</v>
+        <v>212</v>
       </c>
       <c r="H22">
-        <v>262</v>
+        <v>121</v>
       </c>
       <c r="I22">
-        <v>117</v>
+        <v>375</v>
       </c>
       <c r="J22">
-        <v>189</v>
+        <v>289</v>
       </c>
       <c r="K22">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="L22">
-        <v>267</v>
+        <v>50</v>
       </c>
       <c r="M22">
-        <v>-260</v>
+        <v>-298</v>
       </c>
       <c r="N22">
-        <v>-184</v>
+        <v>-49</v>
       </c>
       <c r="O22">
-        <v>-108</v>
+        <v>-380</v>
       </c>
       <c r="P22">
-        <v>265</v>
+        <v>124</v>
       </c>
       <c r="Q22">
-        <v>338</v>
+        <v>201</v>
       </c>
       <c r="R22">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="S22">
-        <v>-32</v>
+        <v>-128</v>
       </c>
       <c r="T22">
-        <v>-116</v>
+        <v>-216</v>
       </c>
       <c r="U22">
-        <v>-194</v>
+        <v>-41</v>
       </c>
       <c r="V22">
-        <v>187</v>
+        <v>292</v>
       </c>
       <c r="W22">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="X22">
-        <v>331</v>
+        <v>210</v>
       </c>
       <c r="Y22">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="Z22">
         <v>180</v>
       </c>
       <c r="AA22">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AB22">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AC22">
         <v>0</v>
       </c>
       <c r="AD22">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AE22">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AF22">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AG22">
         <v>0</v>
       </c>
       <c r="AH22">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ22">
         <v>90</v>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -4601,7 +4606,7 @@
         </is>
       </c>
       <c r="AW22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
@@ -4610,120 +4615,125 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>old</t>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>new</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>-270</v>
+        <v>-282</v>
       </c>
       <c r="B23">
-        <v>-343</v>
+        <v>-132</v>
       </c>
       <c r="C23">
-        <v>-41</v>
+        <v>-44</v>
       </c>
       <c r="D23">
-        <v>-186</v>
+        <v>-203</v>
       </c>
       <c r="E23">
-        <v>-263</v>
+        <v>-130</v>
       </c>
       <c r="F23">
-        <v>-332</v>
+        <v>-40</v>
       </c>
       <c r="G23">
-        <v>255</v>
+        <v>38</v>
       </c>
       <c r="H23">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="I23">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="J23">
-        <v>259</v>
+        <v>202</v>
       </c>
       <c r="K23">
-        <v>335</v>
+        <v>49</v>
       </c>
       <c r="L23">
-        <v>43</v>
+        <v>288</v>
       </c>
       <c r="M23">
-        <v>-185</v>
+        <v>-132</v>
       </c>
       <c r="N23">
-        <v>-118</v>
+        <v>-200</v>
       </c>
       <c r="O23">
-        <v>-262</v>
+        <v>-40</v>
       </c>
       <c r="P23">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="Q23">
-        <v>36</v>
+        <v>203</v>
       </c>
       <c r="R23">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="S23">
-        <v>-109</v>
+        <v>-367</v>
       </c>
       <c r="T23">
-        <v>-333</v>
+        <v>-117</v>
       </c>
       <c r="U23">
-        <v>-36</v>
+        <v>-212</v>
       </c>
       <c r="V23">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="W23">
-        <v>268</v>
+        <v>128</v>
       </c>
       <c r="X23">
-        <v>336</v>
+        <v>290</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Z23">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AA23">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AC23">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AD23">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AE23">
         <v>180</v>
       </c>
       <c r="AF23">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AG23">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AH23">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AJ23">
         <v>0</v>
@@ -4740,19 +4750,19 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AP23" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -4789,7 +4799,7 @@
         </is>
       </c>
       <c r="AW23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
@@ -4798,104 +4808,99 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>new</t>
+          <t>old</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>-182</v>
+        <v>-381</v>
       </c>
       <c r="B24">
-        <v>-269</v>
+        <v>-202</v>
       </c>
       <c r="C24">
-        <v>-109</v>
+        <v>-129</v>
       </c>
       <c r="D24">
-        <v>-193</v>
+        <v>-125</v>
       </c>
       <c r="E24">
-        <v>-332</v>
+        <v>-372</v>
       </c>
       <c r="F24">
-        <v>-45</v>
+        <v>-293</v>
       </c>
       <c r="G24">
-        <v>34</v>
+        <v>374</v>
       </c>
       <c r="H24">
-        <v>266</v>
+        <v>41</v>
       </c>
       <c r="I24">
-        <v>334</v>
+        <v>121</v>
       </c>
       <c r="J24">
-        <v>339</v>
+        <v>288</v>
       </c>
       <c r="K24">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="L24">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="M24">
-        <v>-31</v>
+        <v>-374</v>
       </c>
       <c r="N24">
-        <v>-117</v>
+        <v>-125</v>
       </c>
       <c r="O24">
-        <v>-332</v>
+        <v>-294</v>
       </c>
       <c r="P24">
-        <v>38</v>
+        <v>282</v>
       </c>
       <c r="Q24">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c r="R24">
-        <v>181</v>
+        <v>371</v>
       </c>
       <c r="S24">
-        <v>-31</v>
+        <v>-286</v>
       </c>
       <c r="T24">
-        <v>-333</v>
+        <v>-43</v>
       </c>
       <c r="U24">
-        <v>-266</v>
+        <v>-126</v>
       </c>
       <c r="V24">
+        <v>373</v>
+      </c>
+      <c r="W24">
         <v>36</v>
       </c>
-      <c r="W24">
-        <v>118</v>
-      </c>
       <c r="X24">
-        <v>195</v>
+        <v>123</v>
       </c>
       <c r="Y24">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="Z24">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB24">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AC24">
         <v>90</v>
@@ -4907,19 +4912,19 @@
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AG24">
         <v>90</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AI24">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AJ24">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
@@ -4991,174 +4996,169 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>new</t>
+          <t>old</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>-36</v>
+        <v>-203</v>
       </c>
       <c r="B25">
-        <v>-268</v>
+        <v>-289</v>
       </c>
       <c r="C25">
-        <v>-183</v>
+        <v>-129</v>
       </c>
       <c r="D25">
+        <v>-379</v>
+      </c>
+      <c r="E25">
+        <v>-37</v>
+      </c>
+      <c r="F25">
+        <v>-130</v>
+      </c>
+      <c r="G25">
+        <v>367</v>
+      </c>
+      <c r="H25">
+        <v>202</v>
+      </c>
+      <c r="I25">
+        <v>294</v>
+      </c>
+      <c r="J25">
+        <v>203</v>
+      </c>
+      <c r="K25">
+        <v>296</v>
+      </c>
+      <c r="L25">
+        <v>123</v>
+      </c>
+      <c r="M25">
+        <v>-379</v>
+      </c>
+      <c r="N25">
+        <v>-207</v>
+      </c>
+      <c r="O25">
+        <v>-47</v>
+      </c>
+      <c r="P25">
+        <v>43</v>
+      </c>
+      <c r="Q25">
+        <v>368</v>
+      </c>
+      <c r="R25">
+        <v>290</v>
+      </c>
+      <c r="S25">
         <v>-42</v>
       </c>
-      <c r="E25">
-        <v>-264</v>
-      </c>
-      <c r="F25">
-        <v>-180</v>
-      </c>
-      <c r="G25">
-        <v>106</v>
-      </c>
-      <c r="H25">
-        <v>43</v>
-      </c>
-      <c r="I25">
-        <v>337</v>
-      </c>
-      <c r="J25">
-        <v>334</v>
-      </c>
-      <c r="K25">
-        <v>37</v>
-      </c>
-      <c r="L25">
-        <v>106</v>
-      </c>
-      <c r="M25">
-        <v>-33</v>
-      </c>
-      <c r="N25">
-        <v>-110</v>
-      </c>
-      <c r="O25">
-        <v>-257</v>
-      </c>
-      <c r="P25">
-        <v>336</v>
-      </c>
-      <c r="Q25">
-        <v>268</v>
-      </c>
-      <c r="R25">
-        <v>38</v>
-      </c>
-      <c r="S25">
-        <v>-261</v>
-      </c>
       <c r="T25">
-        <v>-115</v>
+        <v>-294</v>
       </c>
       <c r="U25">
-        <v>-187</v>
+        <v>-381</v>
       </c>
       <c r="V25">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="W25">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c r="X25">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Y25">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="Z25">
         <v>90</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB25">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AC25">
         <v>270</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AE25">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AF25">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AG25">
         <v>270</v>
       </c>
       <c r="AH25">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ25">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -5175,11 +5175,11 @@
         </is>
       </c>
       <c r="AW25">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
